--- a/carbon_constraint.xlsx
+++ b/carbon_constraint.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hy4174/Documents/GitHub/GCAM_USA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B99D84-BFD9-3340-81AB-B870A2A14E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ADA38F-5F63-1941-99DE-A7B24E92894F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18300" yWindow="5760" windowWidth="27240" windowHeight="16440" xr2:uid="{CD997A8A-CBA1-F948-B390-49E2E92F265C}"/>
+    <workbookView xWindow="34600" yWindow="1840" windowWidth="26200" windowHeight="16440" xr2:uid="{CD997A8A-CBA1-F948-B390-49E2E92F265C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>scenario</t>
   </si>
@@ -66,13 +66,25 @@
   </si>
   <si>
     <t>stick + shock</t>
+  </si>
+  <si>
+    <t>trade base stick</t>
+  </si>
+  <si>
+    <t>2005 CO2 emission</t>
+  </si>
+  <si>
+    <t>EIA</t>
+  </si>
+  <si>
+    <t>Energy-Related Carbon Dioxide Emissions by State, 2005-2016</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -91,6 +103,13 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -114,10 +133,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F348AE-3E3A-F44A-97FA-98DAAA2E2B1D}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
@@ -824,6 +844,55 @@
         <v>1141</v>
       </c>
     </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30">
+        <f>5991*0.83</f>
+        <v>4972.53</v>
+      </c>
+      <c r="C30">
+        <f>5991*0.72</f>
+        <v>4313.5199999999995</v>
+      </c>
+      <c r="D30">
+        <f>5991*0.48</f>
+        <v>2875.68</v>
+      </c>
+      <c r="E30">
+        <f>0.34*5991</f>
+        <v>2036.94</v>
+      </c>
+      <c r="F30">
+        <f>E30-H32</f>
+        <v>1641.2933333333333</v>
+      </c>
+      <c r="G30">
+        <f>E30-H32*2</f>
+        <v>1245.6466666666665</v>
+      </c>
+      <c r="H30">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32">
+        <f>(E30-H30)/3</f>
+        <v>395.6466666666667</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B33" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/carbon_constraint.xlsx
+++ b/carbon_constraint.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hy4174/Documents/GitHub/GCAM_USA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ADA38F-5F63-1941-99DE-A7B24E92894F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0637A5C1-B550-2B40-9C26-52386DB86C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34600" yWindow="1840" windowWidth="26200" windowHeight="16440" xr2:uid="{CD997A8A-CBA1-F948-B390-49E2E92F265C}"/>
+    <workbookView xWindow="0" yWindow="1600" windowWidth="34560" windowHeight="19660" activeTab="3" xr2:uid="{CD997A8A-CBA1-F948-B390-49E2E92F265C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ROW" sheetId="2" r:id="rId2"/>
+    <sheet name="Transport" sheetId="4" r:id="rId3"/>
+    <sheet name="Transport_ratio" sheetId="5" r:id="rId4"/>
+    <sheet name="Power" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
   <si>
     <t>scenario</t>
   </si>
@@ -59,9 +63,6 @@
     <t>trade_base_tariff_shock</t>
   </si>
   <si>
-    <t>stick</t>
-  </si>
-  <si>
     <t>power</t>
   </si>
   <si>
@@ -78,6 +79,30 @@
   </si>
   <si>
     <t>Energy-Related Carbon Dioxide Emissions by State, 2005-2016</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>trade_base_stick_onshore</t>
+  </si>
+  <si>
+    <t>trade_base_stick_onshore_chaos</t>
+  </si>
+  <si>
+    <t>trade_base_stick_tariff_chaos</t>
+  </si>
+  <si>
+    <t>trade_base_stick_tariff_current</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>https://cfpub.epa.gov/ghgdata/inventoryexplorer/#allsectors/allsectors/allgas/gas/all</t>
+  </si>
+  <si>
+    <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://www.energy.gov/articles/microsoft-word-fact-sheet-environment-100808-finaldoc#:~:text=Reduce%20Carbon%20Emissions%2080%20Percent,profitable%20manner%20available%20to%20them.</t>
   </si>
 </sst>
 </file>
@@ -472,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F348AE-3E3A-F44A-97FA-98DAAA2E2B1D}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
@@ -513,30 +538,30 @@
       </c>
       <c r="C2">
         <f>$B$13+($H$13-$B$13)/6</f>
-        <v>3887.5</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>$B$13+($H$13-$B$13)/6*2</f>
-        <v>3350</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f>$B$13+($H$13-$B$13)/6*3</f>
-        <v>2812.5</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <f>$B$13+($H$13-$B$13)/6*4</f>
-        <v>2275</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <f>$B$13+($H$13-$B$13)/6*5</f>
-        <v>1737.5</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>1200</v>
       </c>
       <c r="I2">
         <f>SUM(C$2:H$2)</f>
-        <v>15262.5</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -552,22 +577,22 @@
       </c>
       <c r="F3">
         <f>C3-J3</f>
-        <v>4005.5197810956047</v>
+        <v>1661.7697810956047</v>
       </c>
       <c r="G3">
         <f>C3-J3*2</f>
-        <v>3625.7302189043953</v>
+        <v>-1061.7697810956042</v>
       </c>
       <c r="H3">
         <v>1200</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I6" si="0">SUM(C$2:H$2)</f>
-        <v>15262.5</v>
+        <v>1200</v>
       </c>
       <c r="J3">
         <f>(4*C3-I3)/6</f>
-        <v>379.78956219120909</v>
+        <v>2723.5395621912089</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -583,22 +608,22 @@
       </c>
       <c r="F4">
         <f>C4-J4</f>
-        <v>4001.8909544265912</v>
+        <v>1658.1409544265912</v>
       </c>
       <c r="G4">
         <f>C4-J4*2</f>
-        <v>3629.3590455734088</v>
+        <v>-1058.1409544265907</v>
       </c>
       <c r="H4">
         <v>1200</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>15262.5</v>
+        <v>1200</v>
       </c>
       <c r="J4">
         <f>(4*C4-I4)/6</f>
-        <v>372.53190885318207</v>
+        <v>2716.2819088531819</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -614,22 +639,22 @@
       </c>
       <c r="F5">
         <f>C5-J5</f>
-        <v>4002.2938072893112</v>
+        <v>1658.5438072893112</v>
       </c>
       <c r="G5">
         <f>C5-J5*2</f>
-        <v>3628.9561927106888</v>
+        <v>-1058.5438072893112</v>
       </c>
       <c r="H5">
         <v>1200</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>15262.5</v>
+        <v>1200</v>
       </c>
       <c r="J5">
         <f>(4*C5-I5)/6</f>
-        <v>373.33761457862238</v>
+        <v>2717.0876145786224</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -645,22 +670,22 @@
       </c>
       <c r="F6">
         <f>C6-J6</f>
-        <v>4006.4171655341293</v>
+        <v>1662.6671655341293</v>
       </c>
       <c r="G6">
         <f>C6-J6*2</f>
-        <v>3624.8328344658707</v>
+        <v>-1062.6671655341288</v>
       </c>
       <c r="H6">
         <v>1200</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>15262.5</v>
+        <v>1200</v>
       </c>
       <c r="J6">
         <f>(4*C6-I6)/6</f>
-        <v>381.58433106825822</v>
+        <v>2725.3343310682581</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -690,55 +715,24 @@
       <c r="A11" t="s">
         <v>5</v>
       </c>
+      <c r="D11">
+        <v>3519.9981998241951</v>
+      </c>
       <c r="E11">
-        <v>1100.1550466245901</v>
+        <v>2935.9998643424074</v>
       </c>
       <c r="F11">
-        <v>845.45462362010596</v>
+        <v>2351.0005296552958</v>
       </c>
       <c r="G11">
-        <v>586.36398681346498</v>
+        <v>1765.9876117956017</v>
       </c>
       <c r="H11">
-        <v>327.27296406316299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H12">
-        <f>H11*44/12</f>
-        <v>1200.0008682315977</v>
+        <v>1182.0006212248591</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1">
-        <v>4425</v>
-      </c>
-      <c r="C13">
-        <f>$B$13+($H$13-$B$13)/6</f>
-        <v>3887.5</v>
-      </c>
-      <c r="D13">
-        <f>$B$13+($H$13-$B$13)/6*2</f>
-        <v>3350</v>
-      </c>
-      <c r="E13">
-        <f>$B$13+($H$13-$B$13)/6*3</f>
-        <v>2812.5</v>
-      </c>
-      <c r="F13">
-        <f>$B$13+($H$13-$B$13)/6*4</f>
-        <v>2275</v>
-      </c>
-      <c r="G13">
-        <f>$B$13+($H$13-$B$13)/6*5</f>
-        <v>1737.5</v>
-      </c>
-      <c r="H13">
-        <v>1200</v>
-      </c>
+      <c r="B13" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E16">
@@ -758,9 +752,9 @@
         <f>G18*44/12</f>
         <v>2150.0012849333334</v>
       </c>
-      <c r="H17">
-        <f>H12</f>
-        <v>1200.0008682315977</v>
+      <c r="H17" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -776,7 +770,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>170</v>
@@ -811,14 +805,14 @@
         <f t="shared" ref="G23:H23" si="2">G17-G22</f>
         <v>1838.3346182666667</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="e">
         <f t="shared" si="2"/>
-        <v>1200.0008682315977</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26">
         <v>3114</v>
@@ -844,53 +838,520 @@
         <v>1141</v>
       </c>
     </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>2020</v>
+      </c>
+      <c r="C29">
+        <v>2025</v>
+      </c>
+      <c r="D29">
+        <v>2030</v>
+      </c>
+      <c r="E29">
+        <v>2035</v>
+      </c>
+      <c r="F29">
+        <v>2040</v>
+      </c>
+      <c r="G29">
+        <v>2045</v>
+      </c>
+      <c r="H29">
+        <v>2050</v>
+      </c>
+    </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B30">
-        <f>5991*0.83</f>
-        <v>4972.53</v>
+        <v>4689</v>
       </c>
       <c r="C30">
-        <f>5991*0.72</f>
-        <v>4313.5199999999995</v>
+        <f>$B30-$H$32*C31</f>
+        <v>4104.5533333333333</v>
       </c>
       <c r="D30">
-        <f>5991*0.48</f>
-        <v>2875.68</v>
+        <f t="shared" ref="D30:G30" si="4">$B30-$H$32*D31</f>
+        <v>3520.1066666666666</v>
       </c>
       <c r="E30">
-        <f>0.34*5991</f>
-        <v>2036.94</v>
+        <f t="shared" si="4"/>
+        <v>2935.6600000000003</v>
       </c>
       <c r="F30">
-        <f>E30-H32</f>
-        <v>1641.2933333333333</v>
+        <f t="shared" si="4"/>
+        <v>2351.2133333333336</v>
       </c>
       <c r="G30">
-        <f>E30-H32*2</f>
-        <v>1245.6466666666665</v>
+        <f t="shared" si="4"/>
+        <v>1766.7666666666669</v>
       </c>
       <c r="H30">
-        <v>850</v>
+        <f>C32*0.2</f>
+        <v>1182.3200000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="H31">
+        <f>G30-H30</f>
+        <v>584.44666666666672</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s">
         <v>11</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32">
+        <v>5911.6</v>
+      </c>
+      <c r="H32">
+        <f>(B30-H30)/6</f>
+        <v>584.4466666666666</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H32">
-        <f>(E30-H30)/3</f>
-        <v>395.6466666666667</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33" s="3" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35">
+        <v>1990</v>
+      </c>
+      <c r="C35">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EADD9BAC-F44A-B042-8606-39BF092488C6}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2035</v>
+      </c>
+      <c r="B2">
+        <v>1047</v>
+      </c>
+      <c r="C2">
+        <v>979</v>
+      </c>
+      <c r="D2">
+        <v>979</v>
+      </c>
+      <c r="E2">
+        <v>982</v>
+      </c>
+      <c r="F2">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2040</v>
+      </c>
+      <c r="B3">
+        <v>233</v>
+      </c>
+      <c r="C3">
+        <v>227</v>
+      </c>
+      <c r="D3">
+        <v>227</v>
+      </c>
+      <c r="E3">
+        <v>229</v>
+      </c>
+      <c r="F3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2045</v>
+      </c>
+      <c r="B4">
+        <v>-581</v>
+      </c>
+      <c r="C4">
+        <v>-525</v>
+      </c>
+      <c r="D4">
+        <v>-525</v>
+      </c>
+      <c r="E4">
+        <v>-524</v>
+      </c>
+      <c r="F4">
+        <v>-525</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2050</v>
+      </c>
+      <c r="B5">
+        <v>-1277</v>
+      </c>
+      <c r="C5">
+        <v>-1277</v>
+      </c>
+      <c r="D5">
+        <v>-1277</v>
+      </c>
+      <c r="E5">
+        <v>-1277</v>
+      </c>
+      <c r="F5">
+        <v>-1277</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EADD6581-ABE0-894C-862F-B3238A3B1F0E}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2035</v>
+      </c>
+      <c r="B2">
+        <v>1349</v>
+      </c>
+      <c r="C2">
+        <v>1344</v>
+      </c>
+      <c r="D2">
+        <v>1326</v>
+      </c>
+      <c r="E2">
+        <v>1341</v>
+      </c>
+      <c r="F2">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2040</v>
+      </c>
+      <c r="B3">
+        <v>1268</v>
+      </c>
+      <c r="C3">
+        <v>1265</v>
+      </c>
+      <c r="D3">
+        <v>1253</v>
+      </c>
+      <c r="E3">
+        <v>1263</v>
+      </c>
+      <c r="F3">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2045</v>
+      </c>
+      <c r="B4">
+        <v>1188</v>
+      </c>
+      <c r="C4">
+        <v>1186</v>
+      </c>
+      <c r="D4">
+        <v>1180</v>
+      </c>
+      <c r="E4">
+        <v>1185</v>
+      </c>
+      <c r="F4">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2050</v>
+      </c>
+      <c r="B5">
+        <v>1107</v>
+      </c>
+      <c r="C5">
+        <v>1107</v>
+      </c>
+      <c r="D5">
+        <v>1107</v>
+      </c>
+      <c r="E5">
+        <v>1107</v>
+      </c>
+      <c r="F5">
+        <v>1107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21DD6E32-F026-184F-94F0-1DE218253176}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2020</v>
+      </c>
+      <c r="B2">
+        <v>0.95502441217969603</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>0.9550128662692976</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2030</v>
+      </c>
+      <c r="B4">
+        <v>0.95413516411177735</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2035</v>
+      </c>
+      <c r="B5">
+        <v>0.89040295010299508</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2040</v>
+      </c>
+      <c r="B6">
+        <v>0.76418774398103828</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2045</v>
+      </c>
+      <c r="B7">
+        <v>0.62734636716359615</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2050</v>
+      </c>
+      <c r="B8">
+        <v>0.52227730124071803</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{197D77EE-A884-3247-830B-2433765EFEA2}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2035</v>
+      </c>
+      <c r="B2">
+        <v>89</v>
+      </c>
+      <c r="C2">
+        <v>84</v>
+      </c>
+      <c r="D2">
+        <v>86</v>
+      </c>
+      <c r="E2">
+        <v>85</v>
+      </c>
+      <c r="F2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2040</v>
+      </c>
+      <c r="B3">
+        <v>59</v>
+      </c>
+      <c r="C3">
+        <v>56</v>
+      </c>
+      <c r="D3">
+        <v>57</v>
+      </c>
+      <c r="E3">
+        <v>57</v>
+      </c>
+      <c r="F3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2045</v>
+      </c>
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>28</v>
+      </c>
+      <c r="D4">
+        <v>29</v>
+      </c>
+      <c r="E4">
+        <v>28</v>
+      </c>
+      <c r="F4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2050</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
